--- a/artfynd/A 52096-2025 artfynd.xlsx
+++ b/artfynd/A 52096-2025 artfynd.xlsx
@@ -1660,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129874127</v>
+        <v>129874560</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>796471</v>
+        <v>796565</v>
       </c>
       <c r="R11" t="n">
-        <v>7161799</v>
+        <v>7161780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>hackat hål i torraka</t>
+          <t>äldre ringhack på en gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129874560</v>
+        <v>129874387</v>
       </c>
       <c r="B12" t="n">
         <v>57736</v>
@@ -1803,7 +1803,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>796565</v>
+        <v>796469</v>
       </c>
       <c r="R12" t="n">
-        <v>7161780</v>
+        <v>7161781</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>äldre ringhack på en gammal gran</t>
+          <t>fläkt bark på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129874387</v>
+        <v>129874127</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,16 +1891,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1913,7 +1913,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>796469</v>
+        <v>796471</v>
       </c>
       <c r="R13" t="n">
-        <v>7161781</v>
+        <v>7161799</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>fläkt bark på gran</t>
+          <t>hackat hål i torraka</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 52096-2025 artfynd.xlsx
+++ b/artfynd/A 52096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129873974</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129874573</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129867661</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129874563</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>129874558</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129874577</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>129874072</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129867874</v>
       </c>
       <c r="B9" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>129873978</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129874560</v>
+        <v>129874127</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57734</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>796565</v>
+        <v>796471</v>
       </c>
       <c r="R11" t="n">
-        <v>7161780</v>
+        <v>7161799</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>äldre ringhack på en gammal gran</t>
+          <t>hackat hål i torraka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129874387</v>
+        <v>129874560</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>796469</v>
+        <v>796565</v>
       </c>
       <c r="R12" t="n">
-        <v>7161781</v>
+        <v>7161780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>fläkt bark på gran</t>
+          <t>äldre ringhack på en gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129874127</v>
+        <v>129874387</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,16 +1891,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1913,7 +1913,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>796471</v>
+        <v>796469</v>
       </c>
       <c r="R13" t="n">
-        <v>7161799</v>
+        <v>7161781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>hackat hål i torraka</t>
+          <t>fläkt bark på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 52096-2025 artfynd.xlsx
+++ b/artfynd/A 52096-2025 artfynd.xlsx
@@ -1110,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129874558</v>
+        <v>129874577</v>
       </c>
       <c r="B6" t="n">
         <v>57737</v>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>796520</v>
+        <v>796420</v>
       </c>
       <c r="R6" t="n">
-        <v>7161733</v>
+        <v>7161901</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>fläkt bark på klen gran</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129874577</v>
+        <v>129874558</v>
       </c>
       <c r="B7" t="n">
         <v>57737</v>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>796420</v>
+        <v>796520</v>
       </c>
       <c r="R7" t="n">
-        <v>7161901</v>
+        <v>7161733</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>fläkt bark på klen gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1660,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129874127</v>
+        <v>129874560</v>
       </c>
       <c r="B11" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>796471</v>
+        <v>796565</v>
       </c>
       <c r="R11" t="n">
-        <v>7161799</v>
+        <v>7161780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>hackat hål i torraka</t>
+          <t>äldre ringhack på en gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129874560</v>
+        <v>129874387</v>
       </c>
       <c r="B12" t="n">
         <v>57737</v>
@@ -1803,7 +1803,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>796565</v>
+        <v>796469</v>
       </c>
       <c r="R12" t="n">
-        <v>7161780</v>
+        <v>7161781</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>äldre ringhack på en gammal gran</t>
+          <t>fläkt bark på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129874387</v>
+        <v>129874127</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57734</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,16 +1891,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1913,7 +1913,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>796469</v>
+        <v>796471</v>
       </c>
       <c r="R13" t="n">
-        <v>7161781</v>
+        <v>7161799</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>fläkt bark på gran</t>
+          <t>hackat hål i torraka</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 52096-2025 artfynd.xlsx
+++ b/artfynd/A 52096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129873974</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129874573</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129867661</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129874563</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129874577</v>
+        <v>129874558</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>796420</v>
+        <v>796520</v>
       </c>
       <c r="R6" t="n">
-        <v>7161901</v>
+        <v>7161733</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>fläkt bark på klen gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129874558</v>
+        <v>129874577</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>796520</v>
+        <v>796420</v>
       </c>
       <c r="R7" t="n">
-        <v>7161733</v>
+        <v>7161901</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>fläkt bark på klen gran</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,7 +1333,7 @@
         <v>129874072</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129867874</v>
       </c>
       <c r="B9" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>129873978</v>
       </c>
       <c r="B10" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129874560</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>129874387</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129874127</v>
       </c>
       <c r="B13" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52096-2025 artfynd.xlsx
+++ b/artfynd/A 52096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129873974</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129867874</v>
       </c>
       <c r="B9" t="n">
-        <v>82924</v>
+        <v>82925</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129874560</v>
+        <v>129874127</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>796565</v>
+        <v>796471</v>
       </c>
       <c r="R11" t="n">
-        <v>7161780</v>
+        <v>7161799</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>äldre ringhack på en gammal gran</t>
+          <t>hackat hål i torraka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129874387</v>
+        <v>129874560</v>
       </c>
       <c r="B12" t="n">
         <v>57740</v>
@@ -1803,7 +1803,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>796469</v>
+        <v>796565</v>
       </c>
       <c r="R12" t="n">
-        <v>7161781</v>
+        <v>7161780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>fläkt bark på gran</t>
+          <t>äldre ringhack på en gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129874127</v>
+        <v>129874387</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,16 +1891,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1913,7 +1913,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>796471</v>
+        <v>796469</v>
       </c>
       <c r="R13" t="n">
-        <v>7161799</v>
+        <v>7161781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>hackat hål i torraka</t>
+          <t>fläkt bark på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 52096-2025 artfynd.xlsx
+++ b/artfynd/A 52096-2025 artfynd.xlsx
@@ -1660,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129874127</v>
+        <v>129874560</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>796471</v>
+        <v>796565</v>
       </c>
       <c r="R11" t="n">
-        <v>7161799</v>
+        <v>7161780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>hackat hål i torraka</t>
+          <t>äldre ringhack på en gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129874560</v>
+        <v>129874387</v>
       </c>
       <c r="B12" t="n">
         <v>57740</v>
@@ -1803,7 +1803,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>796565</v>
+        <v>796469</v>
       </c>
       <c r="R12" t="n">
-        <v>7161780</v>
+        <v>7161781</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>äldre ringhack på en gammal gran</t>
+          <t>fläkt bark på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129874387</v>
+        <v>129874127</v>
       </c>
       <c r="B13" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,16 +1891,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1913,7 +1913,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>796469</v>
+        <v>796471</v>
       </c>
       <c r="R13" t="n">
-        <v>7161781</v>
+        <v>7161799</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>fläkt bark på gran</t>
+          <t>hackat hål i torraka</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 52096-2025 artfynd.xlsx
+++ b/artfynd/A 52096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129873974</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129867661</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129867874</v>
       </c>
       <c r="B9" t="n">
-        <v>82925</v>
+        <v>82931</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129874560</v>
+        <v>129874127</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>796565</v>
+        <v>796471</v>
       </c>
       <c r="R11" t="n">
-        <v>7161780</v>
+        <v>7161799</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>äldre ringhack på en gammal gran</t>
+          <t>hackat hål i torraka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129874387</v>
+        <v>129874560</v>
       </c>
       <c r="B12" t="n">
         <v>57740</v>
@@ -1803,7 +1803,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>796469</v>
+        <v>796565</v>
       </c>
       <c r="R12" t="n">
-        <v>7161781</v>
+        <v>7161780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>fläkt bark på gran</t>
+          <t>äldre ringhack på en gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129874127</v>
+        <v>129874387</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,16 +1891,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1913,7 +1913,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>796471</v>
+        <v>796469</v>
       </c>
       <c r="R13" t="n">
-        <v>7161799</v>
+        <v>7161781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>hackat hål i torraka</t>
+          <t>fläkt bark på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 52096-2025 artfynd.xlsx
+++ b/artfynd/A 52096-2025 artfynd.xlsx
@@ -1110,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129874558</v>
+        <v>129874577</v>
       </c>
       <c r="B6" t="n">
         <v>57741</v>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>796520</v>
+        <v>796420</v>
       </c>
       <c r="R6" t="n">
-        <v>7161733</v>
+        <v>7161901</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>fläkt bark på klen gran</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129874577</v>
+        <v>129874558</v>
       </c>
       <c r="B7" t="n">
         <v>57741</v>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>796420</v>
+        <v>796520</v>
       </c>
       <c r="R7" t="n">
-        <v>7161901</v>
+        <v>7161733</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>fläkt bark på klen gran</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 52096-2025 artfynd.xlsx
+++ b/artfynd/A 52096-2025 artfynd.xlsx
@@ -1110,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129874577</v>
+        <v>129874558</v>
       </c>
       <c r="B6" t="n">
         <v>57741</v>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>796420</v>
+        <v>796520</v>
       </c>
       <c r="R6" t="n">
-        <v>7161901</v>
+        <v>7161733</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>fläkt bark på klen gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129874558</v>
+        <v>129874577</v>
       </c>
       <c r="B7" t="n">
         <v>57741</v>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>796520</v>
+        <v>796420</v>
       </c>
       <c r="R7" t="n">
-        <v>7161733</v>
+        <v>7161901</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>fläkt bark på klen gran</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 52096-2025 artfynd.xlsx
+++ b/artfynd/A 52096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129873974</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129874573</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129867661</v>
       </c>
       <c r="B4" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129874563</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>129874558</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129874577</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>129874072</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129867874</v>
       </c>
       <c r="B9" t="n">
-        <v>82939</v>
+        <v>83024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>129873978</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129874127</v>
+        <v>129874560</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>796471</v>
+        <v>796565</v>
       </c>
       <c r="R11" t="n">
-        <v>7161799</v>
+        <v>7161780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>hackat hål i torraka</t>
+          <t>äldre ringhack på en gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129874560</v>
+        <v>129874127</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>796565</v>
+        <v>796471</v>
       </c>
       <c r="R12" t="n">
-        <v>7161780</v>
+        <v>7161799</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>äldre ringhack på en gammal gran</t>
+          <t>hackat hål i torraka</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,7 +1883,7 @@
         <v>129874387</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52096-2025 artfynd.xlsx
+++ b/artfynd/A 52096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129873974</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129874573</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129867661</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>57900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129874563</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1113,7 +1113,7 @@
         <v>129874558</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1223,7 +1223,7 @@
         <v>129874577</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1333,7 +1333,7 @@
         <v>129874072</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1443,7 +1443,7 @@
         <v>129867874</v>
       </c>
       <c r="B9" t="n">
-        <v>83024</v>
+        <v>82939</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>129873978</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129874560</v>
+        <v>129874127</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>57738</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>796565</v>
+        <v>796471</v>
       </c>
       <c r="R11" t="n">
-        <v>7161780</v>
+        <v>7161799</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>äldre ringhack på en gammal gran</t>
+          <t>hackat hål i torraka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129874127</v>
+        <v>129874560</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>796471</v>
+        <v>796565</v>
       </c>
       <c r="R12" t="n">
-        <v>7161799</v>
+        <v>7161780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>hackat hål i torraka</t>
+          <t>äldre ringhack på en gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,7 +1883,7 @@
         <v>129874387</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>

--- a/artfynd/A 52096-2025 artfynd.xlsx
+++ b/artfynd/A 52096-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129873974</v>
+        <v>129867874</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>796513</v>
+        <v>796543</v>
       </c>
       <c r="R2" t="n">
-        <v>7161777</v>
+        <v>7161924</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på stammen av en tall</t>
+          <t>på barken av en över 200 år gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129874573</v>
+        <v>129874291</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,31 +796,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>796459</v>
+        <v>796465</v>
       </c>
       <c r="R3" t="n">
-        <v>7161808</v>
+        <v>7161780</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>på stammen av över 200 år gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,6 +876,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,42 +895,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129867661</v>
+        <v>129873974</v>
       </c>
       <c r="B4" t="n">
-        <v>57900</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -938,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>796464</v>
+        <v>796513</v>
       </c>
       <c r="R4" t="n">
-        <v>7161988</v>
+        <v>7161777</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,12 +975,18 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på stammen av en tall</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1000,27 +1005,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129874563</v>
+        <v>129873978</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1033,7 +1038,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1043,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>796447</v>
+        <v>796485</v>
       </c>
       <c r="R5" t="n">
-        <v>7161820</v>
+        <v>7161805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,14 +1088,14 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>fläkt bark på klen gran</t>
+          <t>hål hackade i gammeltall</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1110,27 +1115,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129874558</v>
+        <v>129874127</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1143,7 +1148,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1153,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>796520</v>
+        <v>796471</v>
       </c>
       <c r="R6" t="n">
-        <v>7161733</v>
+        <v>7161799</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,14 +1198,14 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>fläkt bark på klen gran</t>
+          <t>hackat hål i torraka</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1220,27 +1225,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129874577</v>
+        <v>129874177</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1263,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>796420</v>
+        <v>796452</v>
       </c>
       <c r="R7" t="n">
-        <v>7161901</v>
+        <v>7161790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,14 +1308,14 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1330,27 +1335,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129874072</v>
+        <v>129874212</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1363,7 +1368,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1373,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>796469</v>
+        <v>796457</v>
       </c>
       <c r="R8" t="n">
-        <v>7161794</v>
+        <v>7161786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,14 +1418,14 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>barksprätt i gammelgranar, sannolikt gjort av tretåig hackspett</t>
+          <t>bohål i gammal tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1440,41 +1445,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129867874</v>
+        <v>129874523</v>
       </c>
       <c r="B9" t="n">
-        <v>82939</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>796543</v>
+        <v>796461</v>
       </c>
       <c r="R9" t="n">
-        <v>7161924</v>
+        <v>7161770</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1528,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på barken av en över 200 år gammal gran</t>
+          <t>hålhack i död gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1537,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1550,14 +1555,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129873978</v>
+        <v>129874573</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>796485</v>
+        <v>796459</v>
       </c>
       <c r="R10" t="n">
-        <v>7161805</v>
+        <v>7161808</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1638,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>hål hackade i gammeltall</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129874127</v>
+        <v>129874072</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,16 +1676,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1693,7 +1698,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1703,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>796471</v>
+        <v>796469</v>
       </c>
       <c r="R11" t="n">
-        <v>7161799</v>
+        <v>7161794</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,14 +1748,14 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>hackat hål i torraka</t>
+          <t>barksprätt i gammelgranar, sannolikt gjort av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1770,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129874560</v>
+        <v>129874166</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1808,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1813,10 +1818,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>796565</v>
+        <v>796450</v>
       </c>
       <c r="R12" t="n">
-        <v>7161780</v>
+        <v>7161797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,14 +1858,14 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>äldre ringhack på en gammal gran</t>
+          <t>barkfläk på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -1880,10 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129874387</v>
+        <v>129874234</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>796469</v>
+        <v>796457</v>
       </c>
       <c r="R13" t="n">
-        <v>7161781</v>
+        <v>7161783</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1968,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>fläkt bark på gran</t>
+          <t>fläkt bark på stammen av en klen gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,6 +1992,881 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129874387</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nordost om Furugårdstjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>796469</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7161781</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>fläkt bark på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129874558</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nordost om Furugårdstjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>796520</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7161733</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>fläkt bark på klen gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129874560</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nordost om Furugårdstjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>796565</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7161780</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack på en gammal gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129874563</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nordost om Furugårdstjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>796447</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7161820</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>fläkt bark på klen gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129874577</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nordost om Furugårdstjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>796420</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7161901</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129874582</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nordost om Furugårdstjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>796428</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7161875</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>fläkt bark på gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129874583</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nordost om Furugårdstjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>796422</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7161881</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>fläkt bark på gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129867661</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nordost om Furugårdstjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>796464</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7161988</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52096-2025 artfynd.xlsx
+++ b/artfynd/A 52096-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129867874</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874291</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129873974</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129873978</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874127</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874177</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874212</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874523</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874573</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874072</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1882,6 +1937,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874166</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1992,6 +2052,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874234</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2102,6 +2167,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874387</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2212,6 +2282,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874558</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2322,6 +2397,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874560</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2432,6 +2512,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874563</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2542,6 +2627,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874577</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2652,6 +2742,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874582</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2762,6 +2857,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874583</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2867,8 +2967,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129867661</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>